--- a/12账号分组与引流号对照表.xlsx
+++ b/12账号分组与引流号对照表.xlsx
@@ -459,8 +459,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="55" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -476,7 +476,7 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>标题示例（存货主题）</t>
+          <t>标题公式/示例（必须参照，用《项目》替换实际主题）</t>
         </is>
       </c>
     </row>
@@ -493,7 +493,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>甄嬛传版存货库房管理</t>
+          <t>《项目》超强总结！专治混乱记不住！</t>
         </is>
       </c>
     </row>
@@ -510,7 +510,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>广志超市学存货计价法</t>
+          <t>《项目》超强总结！🏆把分喂到你嘴边！</t>
         </is>
       </c>
     </row>
@@ -527,7 +527,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>存货核算速记清单</t>
+          <t>《项目》核算速记清单</t>
         </is>
       </c>
     </row>
@@ -544,7 +544,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>存货跌价准备最易错</t>
+          <t>《项目》最容易踩的坑</t>
         </is>
       </c>
     </row>
@@ -561,7 +561,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>存货核心考点整理</t>
+          <t>《项目》核心考点超强总结</t>
         </is>
       </c>
     </row>
@@ -585,17 +585,17 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>⑦西游记故事号</t>
+          <t>⑦考前突击必背</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>用师徒四人经历类比知识点</t>
+          <t>考点清单体，悬念/揭秘式标题，讲透底层逻辑（2026-07-02改版，原西游记故事号已停用）</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>取经队伍干粮存货管理</t>
+          <t>独家揭秘！《项目》底层逻辑</t>
         </is>
       </c>
     </row>
@@ -612,7 +612,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>小新家零食过期踩坑</t>
+          <t>中级会计其实很水，《项目》背完保本70+</t>
         </is>
       </c>
     </row>
@@ -629,24 +629,24 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>猫咪图解存货跌价准备</t>
+          <t>一张图讲清楚《项目》整章内容</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>⑩西游记故事号2</t>
+          <t>⑩治愈小狗插图号</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>八戒踩坑视角，专讲错误示范</t>
+          <t>小狗拟人化图解，语气活泼亲切（2026-07-02改版，原西游记故事号2已停用）</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>八戒囤货变质踩坑存货</t>
+          <t>《项目》理清了，其实挺简单的，背完就稳了！</t>
         </is>
       </c>
     </row>
@@ -663,7 +663,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>小新图解发出计价方法</t>
+          <t>《项目》考前必背清单，收藏这一条就够了</t>
         </is>
       </c>
     </row>
@@ -680,7 +680,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>存货考点速查背诵</t>
+          <t>《项目》考点速查背诵，收藏这条，比你多刷十道题有用</t>
         </is>
       </c>
     </row>
